--- a/excel_templates/hedging.xlsx
+++ b/excel_templates/hedging.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="15105" windowHeight="8070"/>
+    <workbookView windowWidth="18330" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="提前锁汇" sheetId="24" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <t>委 托 方</t>
   </si>
   <si>
-    <t>{{Proxy client}}</t>
+    <t>{{Proxy_client}}</t>
   </si>
   <si>
     <t>受 托 方</t>
@@ -47,7 +47,7 @@
     <t>合同号/发票号</t>
   </si>
   <si>
-    <t>{{Contract No.}}</t>
+    <t>{{Contract_No.}}</t>
   </si>
   <si>
     <t>付汇日期</t>
@@ -199,7 +199,7 @@
     <t>锁汇日期：</t>
   </si>
   <si>
-    <t>"USD"&amp;{{quantity}}*{{unit price}}</t>
+    <t>"USD"&amp;{{quantity}}*{{unit_price}}</t>
   </si>
   <si>
     <t xml:space="preserve">备注：
@@ -464,16 +464,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <name val="Wingdings"/>
       <charset val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C9" s="40">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="D9" s="41"/>
       <c r="E9" s="42" t="s">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="E12" s="58">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="F12" s="55"/>
       <c r="G12" s="55"/>

--- a/excel_templates/hedging.xlsx
+++ b/excel_templates/hedging.xlsx
@@ -47,7 +47,7 @@
     <t>合同号/发票号</t>
   </si>
   <si>
-    <t>{{Contract_No.}}</t>
+    <t>{{Contract_No}}</t>
   </si>
   <si>
     <t>付汇日期</t>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C9" s="40">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D9" s="41"/>
       <c r="E9" s="42" t="s">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="E12" s="58">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="F12" s="55"/>
       <c r="G12" s="55"/>

--- a/excel_templates/hedging.xlsx
+++ b/excel_templates/hedging.xlsx
@@ -256,20 +256,20 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
@@ -460,6 +460,12 @@
     <font>
       <u/>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -469,12 +475,6 @@
       <name val="Wingdings"/>
       <charset val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -670,7 +670,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -735,19 +735,6 @@
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
@@ -1172,7 +1159,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1184,34 +1171,34 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1344,7 +1331,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="53" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
@@ -1370,188 +1357,182 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="28" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="29" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1959,185 +1940,188 @@
       <c r="E3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="11"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7"/>
     </row>
     <row r="4" ht="35.25" customHeight="1" spans="1:8">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="16" t="s">
+      <c r="C4" s="11"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="17"/>
+      <c r="F4" s="14">
+        <f ca="1">TODAY()</f>
+        <v>46100</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="15"/>
     </row>
     <row r="5" ht="27" customHeight="1" spans="1:8">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="20"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" ht="75.95" customHeight="1" spans="1:8">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="25"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30" t="s">
+      <c r="C7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="31"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="33"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
     </row>
     <row r="8" ht="75.95" customHeight="1" spans="1:8">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35" t="s">
+      <c r="A8" s="32"/>
+      <c r="B8" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="38">
         <f ca="1">TODAY()</f>
         <v>46100</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="42" t="s">
+      <c r="D9" s="39"/>
+      <c r="E9" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="44"/>
-      <c r="H9" s="45"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="43"/>
     </row>
     <row r="10" ht="75.95" customHeight="1" spans="1:8">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47" t="s">
+      <c r="A10" s="44"/>
+      <c r="B10" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="49"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="47"/>
     </row>
     <row r="11" ht="94.5" customHeight="1" spans="1:8">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="52" t="s">
+      <c r="B11" s="49"/>
+      <c r="C11" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="52"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="53"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="51"/>
     </row>
     <row r="12" customFormat="1" ht="40.5" customHeight="1" spans="1:8">
-      <c r="A12" s="54"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="57" t="s">
+      <c r="A12" s="52"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="56">
         <f ca="1">TODAY()</f>
         <v>46100</v>
       </c>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="59"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="57"/>
     </row>
     <row r="13" customFormat="1" ht="33" customHeight="1" spans="1:8">
-      <c r="A13" s="60"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="62"/>
+      <c r="A13" s="58"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="60"/>
     </row>
     <row r="14" ht="18.75" spans="1:8">
-      <c r="A14" s="63" t="s">
+      <c r="A14" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="65"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="63"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="66"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="65"/>
+      <c r="A15" s="64"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="63"/>
     </row>
     <row r="16" ht="84" customHeight="1" spans="1:8">
-      <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="70"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="18">
